--- a/1signaalin_esikäsittely.xlsx
+++ b/1signaalin_esikäsittely.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\KURSSIT\Digitaalilaitteiden suunnittelu\Projekti\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\important\AMK\digitaalilaitteidensuunnittelu\Digitaalilaitteiden-suunnittelu-proj\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12633FD8-0E50-4DCE-ACA9-2BF9A55EB716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11880"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,21 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <r>
-      <t>T(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>◦C)</t>
-    </r>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>LM35 OUT (mV/◦C)</t>
   </si>
@@ -63,45 +47,13 @@
     <t>Kaava</t>
   </si>
   <si>
-    <t>Tarkka</t>
-  </si>
-  <si>
     <t>Vastaus</t>
   </si>
   <si>
     <t>R1</t>
   </si>
   <si>
-    <t>-V / 50µA</t>
-  </si>
-  <si>
     <t>240k</t>
-  </si>
-  <si>
-    <r>
-      <t>U</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(mV)</t>
-    </r>
   </si>
   <si>
     <t>Vs(V)</t>
@@ -114,41 +66,6 @@
   </si>
   <si>
     <t>Uout*(R2+R3)=Uin*R3</t>
-  </si>
-  <si>
-    <r>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ჲ)</t>
-    </r>
   </si>
   <si>
     <t>Uout*R2+Uout*R3=Uin*R3</t>
@@ -186,11 +103,57 @@
   <si>
     <t>ulostulojännite(V)</t>
   </si>
+  <si>
+    <r>
+      <t>Jännitteet minimi sekä maksimilämpötiloissa U</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(mV)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Minimi ja maksimilämpötilat T(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>◦C)</t>
+    </r>
+  </si>
+  <si>
+    <t>-U / I</t>
+  </si>
+  <si>
+    <t>Tarkka (Ohm)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -222,7 +185,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -230,17 +193,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -320,15 +415,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>[1]Sheet1!$B$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ulostulojännite(V)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>ulostulojännite(V)</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
@@ -353,388 +440,382 @@
             </c:spPr>
           </c:marker>
           <c:xVal>
-            <c:numRef>
-              <c:f>[1]Sheet1!$A$2:$A$62</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
-                <c:pt idx="0">
-                  <c:v>-300</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-290</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-280</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-270</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-260</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-250</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-240</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-230</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-220</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-210</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-200</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-190</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-180</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>-170</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-160</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>-150</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>-140</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>-130</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>-120</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>-110</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>-100</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>-90</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>-80</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>-70</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-60</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>-50</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>-40</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>-30</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>-20</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>-10</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>90</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>110</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>130</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>140</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>150</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>170</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>180</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>190</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>200</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>210</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>220</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>230</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>240</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>250</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>260</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>270</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>280</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>290</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>300</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="61"/>
+              <c:pt idx="0">
+                <c:v>-300</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>-290</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>-280</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>-270</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>-260</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>-250</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>-240</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>-230</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>-220</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>-210</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>-200</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>-190</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>-180</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>-170</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>-160</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>-150</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>-140</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>-130</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>-120</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>-110</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>-100</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>-90</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>-80</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>-70</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>-60</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>-50</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>-40</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>-30</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>-20</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>-10</c:v>
+              </c:pt>
+              <c:pt idx="30">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="31">
+                <c:v>10</c:v>
+              </c:pt>
+              <c:pt idx="32">
+                <c:v>20</c:v>
+              </c:pt>
+              <c:pt idx="33">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="34">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="35">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="36">
+                <c:v>60</c:v>
+              </c:pt>
+              <c:pt idx="37">
+                <c:v>70</c:v>
+              </c:pt>
+              <c:pt idx="38">
+                <c:v>80</c:v>
+              </c:pt>
+              <c:pt idx="39">
+                <c:v>90</c:v>
+              </c:pt>
+              <c:pt idx="40">
+                <c:v>100</c:v>
+              </c:pt>
+              <c:pt idx="41">
+                <c:v>110</c:v>
+              </c:pt>
+              <c:pt idx="42">
+                <c:v>120</c:v>
+              </c:pt>
+              <c:pt idx="43">
+                <c:v>130</c:v>
+              </c:pt>
+              <c:pt idx="44">
+                <c:v>140</c:v>
+              </c:pt>
+              <c:pt idx="45">
+                <c:v>150</c:v>
+              </c:pt>
+              <c:pt idx="46">
+                <c:v>160</c:v>
+              </c:pt>
+              <c:pt idx="47">
+                <c:v>170</c:v>
+              </c:pt>
+              <c:pt idx="48">
+                <c:v>180</c:v>
+              </c:pt>
+              <c:pt idx="49">
+                <c:v>190</c:v>
+              </c:pt>
+              <c:pt idx="50">
+                <c:v>200</c:v>
+              </c:pt>
+              <c:pt idx="51">
+                <c:v>210</c:v>
+              </c:pt>
+              <c:pt idx="52">
+                <c:v>220</c:v>
+              </c:pt>
+              <c:pt idx="53">
+                <c:v>230</c:v>
+              </c:pt>
+              <c:pt idx="54">
+                <c:v>240</c:v>
+              </c:pt>
+              <c:pt idx="55">
+                <c:v>250</c:v>
+              </c:pt>
+              <c:pt idx="56">
+                <c:v>260</c:v>
+              </c:pt>
+              <c:pt idx="57">
+                <c:v>270</c:v>
+              </c:pt>
+              <c:pt idx="58">
+                <c:v>280</c:v>
+              </c:pt>
+              <c:pt idx="59">
+                <c:v>290</c:v>
+              </c:pt>
+              <c:pt idx="60">
+                <c:v>300</c:v>
+              </c:pt>
+            </c:numLit>
           </c:xVal>
           <c:yVal>
-            <c:numRef>
-              <c:f>[1]Sheet1!$B$2:$B$62</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
-                <c:pt idx="0">
-                  <c:v>3.08</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3.04</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2.95</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2.9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2.85</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2.79</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2.75</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2.7</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2.66</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.58</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2.5299999999999998</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.48</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2.4300000000000002</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2.39</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2.34</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2.29</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2.25</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2.2000000000000002</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2.15</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>2.09</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>2.04</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.99</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1.94</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1.9</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1.84</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.8</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.75</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.71</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.65</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.61</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.49</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.43</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>1.39</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>1.34</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>1.3</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>1.24</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>1.2</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>1.1499999999999999</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>1.1000000000000001</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>1.05</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>0.99</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>0.93</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0.89</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>0.85</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>0.75</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>0.7</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>0.65</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0.61</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0.56000000000000005</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0.48</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0.44</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>0.39</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>0.34</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>0.28999999999999998</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>0.24</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>0.1</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>0.05</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="61"/>
+              <c:pt idx="0">
+                <c:v>3.08</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>3.04</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>2.95</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>2.9</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>2.85</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>2.79</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>2.75</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>2.7</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>2.66</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>2.58</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>2.5299999999999998</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>2.48</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>2.4300000000000002</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>2.39</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>2.34</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>2.29</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>2.25</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>2.2000000000000002</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>2.15</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>2.09</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>2.04</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>1.99</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>1.94</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>1.9</c:v>
+              </c:pt>
+              <c:pt idx="25">
+                <c:v>1.84</c:v>
+              </c:pt>
+              <c:pt idx="26">
+                <c:v>1.8</c:v>
+              </c:pt>
+              <c:pt idx="27">
+                <c:v>1.75</c:v>
+              </c:pt>
+              <c:pt idx="28">
+                <c:v>1.71</c:v>
+              </c:pt>
+              <c:pt idx="29">
+                <c:v>1.65</c:v>
+              </c:pt>
+              <c:pt idx="30">
+                <c:v>1.61</c:v>
+              </c:pt>
+              <c:pt idx="31">
+                <c:v>1.49</c:v>
+              </c:pt>
+              <c:pt idx="32">
+                <c:v>1.43</c:v>
+              </c:pt>
+              <c:pt idx="33">
+                <c:v>1.39</c:v>
+              </c:pt>
+              <c:pt idx="34">
+                <c:v>1.34</c:v>
+              </c:pt>
+              <c:pt idx="35">
+                <c:v>1.3</c:v>
+              </c:pt>
+              <c:pt idx="36">
+                <c:v>1.24</c:v>
+              </c:pt>
+              <c:pt idx="37">
+                <c:v>1.2</c:v>
+              </c:pt>
+              <c:pt idx="38">
+                <c:v>1.1499999999999999</c:v>
+              </c:pt>
+              <c:pt idx="39">
+                <c:v>1.1000000000000001</c:v>
+              </c:pt>
+              <c:pt idx="40">
+                <c:v>1.05</c:v>
+              </c:pt>
+              <c:pt idx="41">
+                <c:v>0.99</c:v>
+              </c:pt>
+              <c:pt idx="42">
+                <c:v>0.93</c:v>
+              </c:pt>
+              <c:pt idx="43">
+                <c:v>0.89</c:v>
+              </c:pt>
+              <c:pt idx="44">
+                <c:v>0.85</c:v>
+              </c:pt>
+              <c:pt idx="45">
+                <c:v>0.8</c:v>
+              </c:pt>
+              <c:pt idx="46">
+                <c:v>0.75</c:v>
+              </c:pt>
+              <c:pt idx="47">
+                <c:v>0.7</c:v>
+              </c:pt>
+              <c:pt idx="48">
+                <c:v>0.65</c:v>
+              </c:pt>
+              <c:pt idx="49">
+                <c:v>0.61</c:v>
+              </c:pt>
+              <c:pt idx="50">
+                <c:v>0.56000000000000005</c:v>
+              </c:pt>
+              <c:pt idx="51">
+                <c:v>0.48</c:v>
+              </c:pt>
+              <c:pt idx="52">
+                <c:v>0.44</c:v>
+              </c:pt>
+              <c:pt idx="53">
+                <c:v>0.39</c:v>
+              </c:pt>
+              <c:pt idx="54">
+                <c:v>0.34</c:v>
+              </c:pt>
+              <c:pt idx="55">
+                <c:v>0.28999999999999998</c:v>
+              </c:pt>
+              <c:pt idx="56">
+                <c:v>0.24</c:v>
+              </c:pt>
+              <c:pt idx="57">
+                <c:v>0.2</c:v>
+              </c:pt>
+              <c:pt idx="58">
+                <c:v>0.15</c:v>
+              </c:pt>
+              <c:pt idx="59">
+                <c:v>0.1</c:v>
+              </c:pt>
+              <c:pt idx="60">
+                <c:v>0.05</c:v>
+              </c:pt>
+            </c:numLit>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
@@ -810,7 +891,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -936,7 +1016,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1612,20 +1691,26 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1348153</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1662478</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -1643,513 +1728,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>ulostulojännite(V)</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>-300</v>
-          </cell>
-          <cell r="B2">
-            <v>3.08</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>-290</v>
-          </cell>
-          <cell r="B3">
-            <v>3.04</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>-280</v>
-          </cell>
-          <cell r="B4">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>-270</v>
-          </cell>
-          <cell r="B5">
-            <v>2.95</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>-260</v>
-          </cell>
-          <cell r="B6">
-            <v>2.9</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>-250</v>
-          </cell>
-          <cell r="B7">
-            <v>2.85</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>-240</v>
-          </cell>
-          <cell r="B8">
-            <v>2.79</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>-230</v>
-          </cell>
-          <cell r="B9">
-            <v>2.75</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>-220</v>
-          </cell>
-          <cell r="B10">
-            <v>2.7</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>-210</v>
-          </cell>
-          <cell r="B11">
-            <v>2.66</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>-200</v>
-          </cell>
-          <cell r="B12">
-            <v>2.58</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>-190</v>
-          </cell>
-          <cell r="B13">
-            <v>2.5299999999999998</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>-180</v>
-          </cell>
-          <cell r="B14">
-            <v>2.48</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>-170</v>
-          </cell>
-          <cell r="B15">
-            <v>2.4300000000000002</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>-160</v>
-          </cell>
-          <cell r="B16">
-            <v>2.39</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>-150</v>
-          </cell>
-          <cell r="B17">
-            <v>2.34</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>-140</v>
-          </cell>
-          <cell r="B18">
-            <v>2.29</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>-130</v>
-          </cell>
-          <cell r="B19">
-            <v>2.25</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>-120</v>
-          </cell>
-          <cell r="B20">
-            <v>2.2000000000000002</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>-110</v>
-          </cell>
-          <cell r="B21">
-            <v>2.15</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>-100</v>
-          </cell>
-          <cell r="B22">
-            <v>2.09</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>-90</v>
-          </cell>
-          <cell r="B23">
-            <v>2.04</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>-80</v>
-          </cell>
-          <cell r="B24">
-            <v>1.99</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>-70</v>
-          </cell>
-          <cell r="B25">
-            <v>1.94</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>-60</v>
-          </cell>
-          <cell r="B26">
-            <v>1.9</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>-50</v>
-          </cell>
-          <cell r="B27">
-            <v>1.84</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>-40</v>
-          </cell>
-          <cell r="B28">
-            <v>1.8</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>-30</v>
-          </cell>
-          <cell r="B29">
-            <v>1.75</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>-20</v>
-          </cell>
-          <cell r="B30">
-            <v>1.71</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>-10</v>
-          </cell>
-          <cell r="B31">
-            <v>1.65</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>0</v>
-          </cell>
-          <cell r="B32">
-            <v>1.61</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>10</v>
-          </cell>
-          <cell r="B33">
-            <v>1.49</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>20</v>
-          </cell>
-          <cell r="B34">
-            <v>1.43</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>30</v>
-          </cell>
-          <cell r="B35">
-            <v>1.39</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>40</v>
-          </cell>
-          <cell r="B36">
-            <v>1.34</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>50</v>
-          </cell>
-          <cell r="B37">
-            <v>1.3</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>60</v>
-          </cell>
-          <cell r="B38">
-            <v>1.24</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>70</v>
-          </cell>
-          <cell r="B39">
-            <v>1.2</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>80</v>
-          </cell>
-          <cell r="B40">
-            <v>1.1499999999999999</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>90</v>
-          </cell>
-          <cell r="B41">
-            <v>1.1000000000000001</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>100</v>
-          </cell>
-          <cell r="B42">
-            <v>1.05</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>110</v>
-          </cell>
-          <cell r="B43">
-            <v>0.99</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>120</v>
-          </cell>
-          <cell r="B44">
-            <v>0.93</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>130</v>
-          </cell>
-          <cell r="B45">
-            <v>0.89</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>140</v>
-          </cell>
-          <cell r="B46">
-            <v>0.85</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>150</v>
-          </cell>
-          <cell r="B47">
-            <v>0.8</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>160</v>
-          </cell>
-          <cell r="B48">
-            <v>0.75</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>170</v>
-          </cell>
-          <cell r="B49">
-            <v>0.7</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>180</v>
-          </cell>
-          <cell r="B50">
-            <v>0.65</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>190</v>
-          </cell>
-          <cell r="B51">
-            <v>0.61</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>200</v>
-          </cell>
-          <cell r="B52">
-            <v>0.56000000000000005</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>210</v>
-          </cell>
-          <cell r="B53">
-            <v>0.48</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>220</v>
-          </cell>
-          <cell r="B54">
-            <v>0.44</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>230</v>
-          </cell>
-          <cell r="B55">
-            <v>0.39</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>240</v>
-          </cell>
-          <cell r="B56">
-            <v>0.34</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>250</v>
-          </cell>
-          <cell r="B57">
-            <v>0.28999999999999998</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58">
-            <v>260</v>
-          </cell>
-          <cell r="B58">
-            <v>0.24</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>270</v>
-          </cell>
-          <cell r="B59">
-            <v>0.2</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>280</v>
-          </cell>
-          <cell r="B60">
-            <v>0.15</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>290</v>
-          </cell>
-          <cell r="B61">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>300</v>
-          </cell>
-          <cell r="B62">
-            <v>0.05</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2414,647 +1992,676 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L80"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="8" max="8" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>-30</v>
+      </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>A2*$C$2</f>
+        <v>-300</v>
+      </c>
+      <c r="B5" s="1">
+        <f>B2*$C$2</f>
+        <v>300</v>
+      </c>
+      <c r="C5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B7" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>-30</v>
-      </c>
-      <c r="B3">
-        <v>30</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3">
+      <c r="B9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="17">
         <f>-(-12)/(50*10^-6)</f>
         <v>240000.00000000003</v>
       </c>
-      <c r="L3" t="s">
+      <c r="D9" s="18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="C11" s="5"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K4">
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="8">
         <f>0.3*10000/(12-0.3)</f>
         <v>256.41025641025641</v>
       </c>
-      <c r="L4">
+      <c r="D16" s="9">
         <v>256</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <f>A3*$D$3</f>
-        <v>-300</v>
-      </c>
-      <c r="B5" s="1">
-        <f>B3*$D$3</f>
-        <v>300</v>
-      </c>
-      <c r="D5">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <f>$D$5/(0.00005)</f>
-        <v>240000</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H8" s="3" t="s">
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H9" s="3" t="s">
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G10" t="s">
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+      <c r="B21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10">
+      <c r="C21" s="8">
         <f>-3/(-0.3-0.3)*10000</f>
         <v>50000</v>
       </c>
-      <c r="L10" t="s">
+      <c r="D21" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H12" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H13" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>-300</v>
       </c>
-      <c r="B20">
+      <c r="B25">
         <v>3.08</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>-290</v>
       </c>
-      <c r="B21">
+      <c r="B26">
         <v>3.04</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>-280</v>
       </c>
-      <c r="B22">
+      <c r="B27">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>-270</v>
       </c>
-      <c r="B23">
+      <c r="B28">
         <v>2.95</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>-260</v>
       </c>
-      <c r="B24">
+      <c r="B29">
         <v>2.9</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>-250</v>
       </c>
-      <c r="B25">
+      <c r="B30">
         <v>2.85</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>-240</v>
       </c>
-      <c r="B26">
+      <c r="B31">
         <v>2.79</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>-230</v>
       </c>
-      <c r="B27">
+      <c r="B32">
         <v>2.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>-220</v>
-      </c>
-      <c r="B28">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>-210</v>
-      </c>
-      <c r="B29">
-        <v>2.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>-200</v>
-      </c>
-      <c r="B30">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>-190</v>
-      </c>
-      <c r="B31">
-        <v>2.5299999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>-180</v>
-      </c>
-      <c r="B32">
-        <v>2.48</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>-170</v>
+        <v>-220</v>
       </c>
       <c r="B33">
-        <v>2.4300000000000002</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>-160</v>
+        <v>-210</v>
       </c>
       <c r="B34">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="B35">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>-140</v>
+        <v>-190</v>
       </c>
       <c r="B36">
-        <v>2.29</v>
+        <v>2.5299999999999998</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>-130</v>
+        <v>-180</v>
       </c>
       <c r="B37">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>-120</v>
+        <v>-170</v>
       </c>
       <c r="B38">
-        <v>2.2000000000000002</v>
+        <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>-110</v>
+        <v>-160</v>
       </c>
       <c r="B39">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="B40">
-        <v>2.09</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>-90</v>
+        <v>-140</v>
       </c>
       <c r="B41">
-        <v>2.04</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>-80</v>
+        <v>-130</v>
       </c>
       <c r="B42">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>-70</v>
+        <v>-120</v>
       </c>
       <c r="B43">
-        <v>1.94</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>-60</v>
+        <v>-110</v>
       </c>
       <c r="B44">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="B45">
-        <v>1.84</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>-40</v>
+        <v>-90</v>
       </c>
       <c r="B46">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>-30</v>
+        <v>-80</v>
       </c>
       <c r="B47">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>-20</v>
+        <v>-70</v>
       </c>
       <c r="B48">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>-10</v>
+        <v>-60</v>
       </c>
       <c r="B49">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="B50">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10</v>
+        <v>-40</v>
       </c>
       <c r="B51">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="B52">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>30</v>
+        <v>-20</v>
       </c>
       <c r="B53">
-        <v>1.39</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>40</v>
+        <v>-10</v>
       </c>
       <c r="B54">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="B55">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="B56">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="B57">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B58">
-        <v>1.1499999999999999</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B59">
-        <v>1.1000000000000001</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B60">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="B61">
-        <v>0.99</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="B62">
-        <v>0.93</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B63">
-        <v>0.89</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="B64">
-        <v>0.85</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B65">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="B66">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="B67">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="B68">
-        <v>0.65</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="B69">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="B70">
-        <v>0.56000000000000005</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="B71">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="B72">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="B73">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>240</v>
+        <v>190</v>
       </c>
       <c r="B74">
-        <v>0.34</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="B75">
-        <v>0.28999999999999998</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="B76">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="B77">
-        <v>0.2</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="B78">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="B79">
-        <v>0.1</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
+        <v>250</v>
+      </c>
+      <c r="B80">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>260</v>
+      </c>
+      <c r="B81">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>270</v>
+      </c>
+      <c r="B82">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>280</v>
+      </c>
+      <c r="B83">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>290</v>
+      </c>
+      <c r="B84">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85">
         <v>300</v>
       </c>
-      <c r="B80">
+      <c r="B85">
         <v>0.05</v>
       </c>
     </row>

--- a/1signaalin_esikäsittely.xlsx
+++ b/1signaalin_esikäsittely.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\important\AMK\digitaalilaitteidensuunnittelu\Digitaalilaitteiden-suunnittelu-proj\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12633FD8-0E50-4DCE-ACA9-2BF9A55EB716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62771A1E-9563-46D0-9CBD-287CC7EEFE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>240k</t>
-  </si>
-  <si>
-    <t>Vs(V)</t>
   </si>
   <si>
     <t>R3</t>
@@ -148,6 +145,9 @@
   </si>
   <si>
     <t>Tarkka (Ohm)</t>
+  </si>
+  <si>
+    <t>Käyttöjännite Vs(V)</t>
   </si>
 </sst>
 </file>
@@ -1997,14 +1997,14 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="7" max="7" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -2023,10 +2023,10 @@
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2050,7 +2050,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -2061,7 +2061,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="17">
         <f>-(-12)/(50*10^-6)</f>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="6"/>
@@ -2088,7 +2088,7 @@
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="13"/>
@@ -2096,7 +2096,7 @@
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="12"/>
       <c r="D13" s="13"/>
@@ -2104,7 +2104,7 @@
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="13"/>
@@ -2112,7 +2112,7 @@
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="13"/>
@@ -2120,7 +2120,7 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" s="8">
         <f>0.3*10000/(12-0.3)</f>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="6"/>
@@ -2143,7 +2143,7 @@
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="13"/>
@@ -2151,7 +2151,7 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="13"/>
@@ -2159,22 +2159,22 @@
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" s="8">
         <f>-3/(-0.3-0.3)*10000</f>
         <v>50000</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
         <v>20</v>
-      </c>
-      <c r="B24" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">

--- a/1signaalin_esikäsittely.xlsx
+++ b/1signaalin_esikäsittely.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\important\AMK\digitaalilaitteidensuunnittelu\Digitaalilaitteiden-suunnittelu-proj\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\KURSSIT\Digitaalilaitteiden suunnittelu\Projekti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62771A1E-9563-46D0-9CBD-287CC7EEFE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BD6166-4359-4BD9-810E-97315399B456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>LM35 OUT (mV/◦C)</t>
   </si>
@@ -101,8 +101,35 @@
     <t>ulostulojännite(V)</t>
   </si>
   <si>
+    <t>-U / I</t>
+  </si>
+  <si>
+    <t>Tarkka (Ohm)</t>
+  </si>
+  <si>
+    <t>Käyttöjännite Vs(V)</t>
+  </si>
+  <si>
+    <t>LM35 käyttövirta negatiivisille jännitteille</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>R2 (Ohm)</t>
+  </si>
+  <si>
+    <t>R4 (Ohm)</t>
+  </si>
+  <si>
+    <t>Ulostulo min UA(V)</t>
+  </si>
+  <si>
+    <t>Ulostulo max UA(V)</t>
+  </si>
+  <si>
     <r>
-      <t>Jännitteet minimi sekä maksimilämpötiloissa U</t>
+      <t>LM35 jännite min U</t>
     </r>
     <r>
       <rPr>
@@ -123,12 +150,38 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(mV)</t>
+      <t>(V)</t>
     </r>
   </si>
   <si>
     <r>
-      <t>Minimi ja maksimilämpötilat T(</t>
+      <t>LM35 jännite max U</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(V)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>lämpötila min T(</t>
     </r>
     <r>
       <rPr>
@@ -141,13 +194,10 @@
     </r>
   </si>
   <si>
-    <t>-U / I</t>
-  </si>
-  <si>
-    <t>Tarkka (Ohm)</t>
-  </si>
-  <si>
-    <t>Käyttöjännite Vs(V)</t>
+    <t>lämpötila max T(◦C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -314,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -328,8 +378,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
@@ -1692,15 +1741,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1662478</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>509953</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1725,6 +1774,111 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>332344</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>76906</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9ACD1AC-6EFF-0074-D543-E1F15067BC52}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5410200" y="3571875"/>
+          <a:ext cx="2646919" cy="2448631"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>95704</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4" descr="voltage divider formula">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6258E1B7-2312-617E-75FF-C9DD06E0D216}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="5419725" y="1914525"/>
+          <a:ext cx="2400754" cy="1504950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1993,7 +2147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -2002,15 +2156,21 @@
     <col min="7" max="7" width="9.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>-30</v>
       </c>
@@ -2020,648 +2180,679 @@
       <c r="C2">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <f>50*10^(-6)</f>
+        <v>4.9999999999999996E-5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <f>A2*$C$2</f>
-        <v>-300</v>
+        <f>A2*$C$2/1000</f>
+        <v>-0.3</v>
       </c>
       <c r="B5" s="1">
-        <f>B2*$C$2</f>
-        <v>300</v>
+        <f>B2*$C$2/1000</f>
+        <v>0.3</v>
       </c>
       <c r="C5">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>10000</v>
+      </c>
+      <c r="F5">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>1</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="17">
-        <f>-(-12)/(50*10^-6)</f>
+      <c r="B11" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="16">
+        <f>-(-C5)/E2</f>
         <v>240000.00000000003</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D11" s="17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="5"/>
+      <c r="D13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="14" t="s">
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="B18" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="8">
-        <f>0.3*10000/(12-0.3)</f>
+      <c r="C18" s="8">
+        <f>B5*E5/(C5-B5)</f>
         <v>256.41025641025641</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D18" s="9">
         <v>256</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11" t="s">
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11" t="s">
+      <c r="D21" s="12"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="14" t="s">
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="7"/>
+      <c r="B23" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="8">
-        <f>-3/(-0.3-0.3)*10000</f>
+      <c r="C23" s="8">
+        <f>-A8/(A5-B5)*F5</f>
         <v>50000</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D23" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>19</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B26" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>-300</v>
-      </c>
-      <c r="B25">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>-290</v>
-      </c>
-      <c r="B26">
-        <v>3.04</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>-280</v>
+        <v>-300</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>-270</v>
+        <v>-290</v>
       </c>
       <c r="B28">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>-260</v>
+        <v>-280</v>
       </c>
       <c r="B29">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>-250</v>
+        <v>-270</v>
       </c>
       <c r="B30">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>-240</v>
+        <v>-260</v>
       </c>
       <c r="B31">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>-230</v>
+        <v>-250</v>
       </c>
       <c r="B32">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>-220</v>
+        <v>-240</v>
       </c>
       <c r="B33">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>-210</v>
+        <v>-230</v>
       </c>
       <c r="B34">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>-200</v>
+        <v>-220</v>
       </c>
       <c r="B35">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>-190</v>
+        <v>-210</v>
       </c>
       <c r="B36">
-        <v>2.5299999999999998</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>-180</v>
+        <v>-200</v>
       </c>
       <c r="B37">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>-170</v>
+        <v>-190</v>
       </c>
       <c r="B38">
-        <v>2.4300000000000002</v>
+        <v>2.5299999999999998</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>-160</v>
+        <v>-180</v>
       </c>
       <c r="B39">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>-150</v>
+        <v>-170</v>
       </c>
       <c r="B40">
-        <v>2.34</v>
+        <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>-140</v>
+        <v>-160</v>
       </c>
       <c r="B41">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>-130</v>
+        <v>-150</v>
       </c>
       <c r="B42">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>-120</v>
+        <v>-140</v>
       </c>
       <c r="B43">
-        <v>2.2000000000000002</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>-110</v>
+        <v>-130</v>
       </c>
       <c r="B44">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>-100</v>
+        <v>-120</v>
       </c>
       <c r="B45">
-        <v>2.09</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>-90</v>
+        <v>-110</v>
       </c>
       <c r="B46">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="B47">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>-70</v>
+        <v>-90</v>
       </c>
       <c r="B48">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="B49">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="B50">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="B51">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="B52">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="B53">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>-10</v>
+        <v>-30</v>
       </c>
       <c r="B54">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="B55">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="B56">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B57">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B58">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="B59">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="B60">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B61">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="B62">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="B63">
-        <v>1.1499999999999999</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B64">
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B65">
-        <v>1.05</v>
+        <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="B66">
-        <v>0.99</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B67">
-        <v>0.93</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B68">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B69">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B70">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="B71">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B72">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="B73">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="B74">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="B75">
-        <v>0.56000000000000005</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="B76">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="B77">
-        <v>0.44</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="B78">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="B79">
-        <v>0.34</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="B80">
-        <v>0.28999999999999998</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="B81">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="B82">
-        <v>0.2</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B83">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="B84">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
+        <v>280</v>
+      </c>
+      <c r="B85">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>290</v>
+      </c>
+      <c r="B86">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87">
         <v>300</v>
       </c>
-      <c r="B85">
+      <c r="B87">
         <v>0.05</v>
       </c>
     </row>
